--- a/banks/W04_Kahoot匯入.xlsx
+++ b/banks/W04_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>伴護蛋白</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>膠原蛋白</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>一級結構</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>球狀蛋白</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>一級結構</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>伴護蛋白</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>膠原蛋白</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -526,30 +526,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>四級結構</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>三級結構</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>伴護蛋白</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>二級結構</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>三級結構</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>伴護蛋白</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>四級結構</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -561,30 +561,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>一級結構</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>三級結構</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>一級結構</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>伴護蛋白</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>膠原蛋白</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>伴護蛋白</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -601,25 +601,25 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>α螺旋</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>四級結構</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>伴護蛋白</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>α螺旋</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>α螺旋</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>角蛋白</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>四級結構</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>β摺板</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>角蛋白</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>α螺旋</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>四級結構</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -666,30 +666,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>球狀蛋白</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>伴護蛋白</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>β摺板</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>伴護蛋白</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>轉角</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>球狀蛋白</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>二級結構</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>摺疊</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>二級結構</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -736,19 +736,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>轉角</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>β摺板</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>摺疊</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>β摺板</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>轉角</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>球狀蛋白</t>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>角蛋白</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>次單元</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>摺疊</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>球狀蛋白</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>次單元</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>角蛋白</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -841,19 +841,19 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>α螺旋</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>結構域</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>二級結構</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>α螺旋</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>結構域</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>次單元</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>β摺板</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>二級結構</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>纖維狀蛋白</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>伴護蛋白</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>二級結構</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>纖維狀蛋白</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>β摺板</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>纖維狀蛋白</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>膠原蛋白</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>球狀蛋白</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>一級結構</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>膠原蛋白</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>纖維狀蛋白</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>球狀蛋白</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>球狀蛋白</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>β摺板</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>膠原蛋白</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>β摺板</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>三級結構</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>球狀蛋白</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>結構域</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>二級結構</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>膠原蛋白</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>一級結構</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>結構域</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1016,30 +1016,30 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>膠原蛋白</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>一級結構</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>次單元</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>角蛋白</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>次單元</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>膠原蛋白</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1051,30 +1051,170 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>X光晶體繞射</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>球狀蛋白</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>二級結構</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>球狀蛋白</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>纖維狀蛋白</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>X光晶體繞射</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:蛋白質結構層次) 標號1所在的胺基酸鏈代表哪一層結構?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>一級結構</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>二級結構</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>四級結構</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>三級結構</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:α螺旋與β摺板) 標號1的虛線代表α螺旋中哪一種鍵?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>離子鍵</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>氫鍵</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>雙硫鍵</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>胜肽鍵</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>三級結構—胺基酸序列本身</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>四級結構—多個次單元組合</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>一級結構—多個次單元組合</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>二級結構—決定胺基酸種類</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>使蛋白質失去原本立體結構、失去功能的過程稱為什麼?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>變性</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>轉角</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>摺疊</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>結構域</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
